--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16D1804-9045-4C1E-9301-0357D464D59F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED9AE9A-909B-4B3F-AA44-A894DCFA3B8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
     <sheet name="05,01" sheetId="117" r:id="rId2"/>
+    <sheet name="05,02" sheetId="118" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'05,02'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -207,8 +209,94 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{F29E28DD-0C54-409B-BABE-6D9C7684B32B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{62637BD7-DDAB-431C-AE19-68A9852C53F3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{79CD2D8C-02B0-48E5-A043-0E4F33888830}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -1816,7 +1904,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2367,6 +2455,21 @@
     <xf numFmtId="167" fontId="9" fillId="5" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="93" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="94" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2435,12 +2538,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="93" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="94" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2812,15 +2909,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="189"/>
-      <c r="Q1" s="190"/>
-      <c r="R1" s="190"/>
-      <c r="S1" s="190"/>
-      <c r="T1" s="190"/>
-      <c r="U1" s="190"/>
-      <c r="V1" s="190"/>
-      <c r="W1" s="190"/>
-      <c r="X1" s="191"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
+      <c r="X1" s="196"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -2845,62 +2942,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="192" t="s">
+      <c r="B4" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="193" t="s">
+      <c r="C4" s="198" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="194" t="s">
+      <c r="D4" s="199" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="195" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="196"/>
-      <c r="G4" s="197" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="199" t="s">
+      <c r="H4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="199" t="s">
+      <c r="J4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
-      <c r="W4" s="204"/>
-      <c r="X4" s="206"/>
+      <c r="M4" s="209"/>
+      <c r="N4" s="209"/>
+      <c r="O4" s="209"/>
+      <c r="P4" s="209"/>
+      <c r="Q4" s="209"/>
+      <c r="R4" s="209"/>
+      <c r="S4" s="209"/>
+      <c r="T4" s="209"/>
+      <c r="U4" s="209"/>
+      <c r="V4" s="210"/>
+      <c r="W4" s="209"/>
+      <c r="X4" s="211"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="192"/>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="B5" s="197"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="199"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="198"/>
-      <c r="H5" s="200"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="200"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="205"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5151,7 +5248,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="184" t="s">
+      <c r="G62" s="189" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5169,7 +5266,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="185"/>
+      <c r="G63" s="190"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5185,7 +5282,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="186"/>
+      <c r="G64" s="191"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5201,7 +5298,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="187" t="s">
+      <c r="G65" s="192" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5219,7 +5316,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="187"/>
+      <c r="G66" s="192"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5235,7 +5332,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="188"/>
+      <c r="G67" s="193"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -5630,17 +5727,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="189">
+      <c r="P1" s="194">
         <v>46204</v>
       </c>
-      <c r="Q1" s="190"/>
-      <c r="R1" s="190"/>
-      <c r="S1" s="190"/>
-      <c r="T1" s="190"/>
-      <c r="U1" s="190"/>
-      <c r="V1" s="190"/>
-      <c r="W1" s="190"/>
-      <c r="X1" s="191"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
+      <c r="X1" s="196"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -5665,62 +5762,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="192" t="s">
+      <c r="B4" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="193" t="s">
+      <c r="C4" s="198" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="194" t="s">
+      <c r="D4" s="199" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="195" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="196"/>
-      <c r="G4" s="197" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="199" t="s">
+      <c r="H4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="199" t="s">
+      <c r="J4" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
-      <c r="W4" s="204"/>
-      <c r="X4" s="206"/>
+      <c r="M4" s="209"/>
+      <c r="N4" s="209"/>
+      <c r="O4" s="209"/>
+      <c r="P4" s="209"/>
+      <c r="Q4" s="209"/>
+      <c r="R4" s="209"/>
+      <c r="S4" s="209"/>
+      <c r="T4" s="209"/>
+      <c r="U4" s="209"/>
+      <c r="V4" s="210"/>
+      <c r="W4" s="209"/>
+      <c r="X4" s="211"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="192"/>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
+      <c r="B5" s="197"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="199"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="198"/>
-      <c r="H5" s="200"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="200"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="205"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5885,19 +5982,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>41</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -5925,7 +6026,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>993</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -5960,7 +6061,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>109</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -5968,7 +6071,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -6000,7 +6103,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2616</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -6035,7 +6138,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>154</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -6043,7 +6148,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -6075,7 +6180,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3696</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -6110,7 +6215,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>120</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -6118,7 +6225,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -6150,7 +6257,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -6185,19 +6292,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -6225,7 +6336,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -6260,47 +6371,61 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3986</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>22</v>
+      </c>
+      <c r="H13" s="79">
+        <v>24</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3964</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121">
+        <v>12</v>
+      </c>
+      <c r="P13" s="121">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>95112</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -6342,19 +6467,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
-        <f t="shared" ref="I9:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -6382,7 +6511,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -6417,7 +6546,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -6425,7 +6556,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -6457,7 +6588,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -6642,7 +6773,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -6650,7 +6783,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -6682,7 +6815,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -6792,19 +6925,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -6832,7 +6969,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -6867,7 +7004,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -6875,7 +7014,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -6907,7 +7046,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -6942,7 +7081,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -6950,7 +7091,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -6982,7 +7123,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -7018,7 +7159,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -7029,7 +7172,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -7057,7 +7200,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -7099,19 +7242,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -7139,7 +7286,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -7181,7 +7328,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -7189,7 +7338,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -7221,7 +7370,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -7256,19 +7405,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>116</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -7296,7 +7449,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2785</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -7371,7 +7524,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -7379,7 +7534,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -7411,7 +7566,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -7430,15 +7585,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>149</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>10</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
@@ -7447,13 +7606,17 @@
       <c r="K29" s="42"/>
       <c r="L29" s="112"/>
       <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
+      <c r="N29" s="112">
+        <v>5</v>
+      </c>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>5</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -7462,15 +7625,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3336</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -7489,30 +7652,40 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>25</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
       <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
+      <c r="N30" s="112">
+        <v>1</v>
+      </c>
       <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
+      <c r="P30" s="112">
+        <v>1</v>
+      </c>
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -7521,15 +7694,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -7541,7 +7714,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>4</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -7549,7 +7724,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -7581,7 +7756,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -7749,19 +7924,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>160</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -7789,7 +7968,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3854</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -7905,30 +8084,38 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4047</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>54</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3993</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>54</v>
+      </c>
       <c r="O38" s="121"/>
       <c r="P38" s="121"/>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -7937,15 +8124,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>23959</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -8061,19 +8248,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>164</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -8101,7 +8292,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3956</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -8113,15 +8304,19 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>75</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>10</v>
+      </c>
       <c r="H42" s="167"/>
-      <c r="I42" s="207">
+      <c r="I42" s="187">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
@@ -8130,13 +8325,17 @@
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>8</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>2</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -8145,15 +8344,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -8208,30 +8407,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>51272</v>
+      </c>
+      <c r="D44" s="114">
+        <v>5</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>634</v>
+      </c>
       <c r="H44" s="79"/>
-      <c r="I44" s="208">
+      <c r="I44" s="188">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>50638</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K44" s="51"/>
       <c r="L44" s="121"/>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>256</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>378</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -8240,15 +8449,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>3804</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>303833</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -8356,7 +8565,9 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="110"/>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
       <c r="D47" s="111"/>
       <c r="E47" s="112"/>
       <c r="F47" s="112"/>
@@ -8364,7 +8575,7 @@
       <c r="H47" s="73"/>
       <c r="I47" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="77">
         <f t="shared" si="7"/>
@@ -8396,7 +8607,7 @@
       </c>
       <c r="W47" s="129">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X47" s="27"/>
     </row>
@@ -8408,19 +8619,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2766</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2766</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -8448,7 +8663,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16597</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -8460,7 +8675,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -8468,7 +8685,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -8500,7 +8717,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -8616,7 +8833,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -8624,7 +8843,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -8656,7 +8875,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -8720,7 +8939,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -8728,7 +8949,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -8760,7 +8981,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -8975,11 +9196,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>63312</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -8988,19 +9209,19 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>62581</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
@@ -9013,40 +9234,40 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>5064</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="W60" s="183">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>467515</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -9054,7 +9275,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="184" t="s">
+      <c r="G62" s="189" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9072,7 +9293,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="185"/>
+      <c r="G63" s="190"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9088,7 +9309,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="186"/>
+      <c r="G64" s="191"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9104,7 +9325,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="187" t="s">
+      <c r="G65" s="192" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9122,7 +9343,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="187"/>
+      <c r="G66" s="192"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9138,7 +9359,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="188"/>
+      <c r="G67" s="193"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -9162,6 +9383,4045 @@
         <v>3</v>
       </c>
       <c r="D69" s="181"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81AD7469-5A1E-48DC-96CF-9185D720F97C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="194">
+        <v>46205</v>
+      </c>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
+      <c r="X1" s="196"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="197" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="198" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="199" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="200" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="204" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="206" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="204" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="208" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="209"/>
+      <c r="N4" s="209"/>
+      <c r="O4" s="209"/>
+      <c r="P4" s="209"/>
+      <c r="Q4" s="209"/>
+      <c r="R4" s="209"/>
+      <c r="S4" s="209"/>
+      <c r="T4" s="209"/>
+      <c r="U4" s="209"/>
+      <c r="V4" s="210"/>
+      <c r="W4" s="209"/>
+      <c r="X4" s="211"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="197"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="186" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="203"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="205"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>41</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>41</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>993</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>109</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>109</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2616</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>154</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>154</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>3696</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>120</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76">
+        <v>2</v>
+      </c>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>118</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112">
+        <v>2</v>
+      </c>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>48</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>2</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>2832</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3963</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>13</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3950</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>-12</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>5</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>13</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>12</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>312</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>94788</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>116</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>1</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>115</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>1</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>2761</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>139</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>2</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>137</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112">
+        <v>2</v>
+      </c>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>3288</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>24</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>557</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>4</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>160</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>159</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112">
+        <v>1</v>
+      </c>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>3830</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3993</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>78</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>3915</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>25</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>53</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>78</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>468</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>78</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>23491</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>164</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>46</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>118</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154">
+        <v>46</v>
+      </c>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>46</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>1104</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>46</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>2852</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>65</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>16</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>49</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>10</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>6</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>192</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>16</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>588</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>50638</v>
+      </c>
+      <c r="D44" s="114">
+        <v>5</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>553</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>50085</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>282</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>271</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>553</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>3318</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>553</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>300515</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>96</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2766</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>2766</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16597</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>62580</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>133</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>713</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>12</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>61867</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>121</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>374</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>339</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>713</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>5562</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>713</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>461941</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="189" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="190"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="191"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="192" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="192"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="193"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="184" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="185"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED9AE9A-909B-4B3F-AA44-A894DCFA3B8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E212B63-5378-4505-AE18-5F9A2A0079EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
     <sheet name="05,01" sheetId="117" r:id="rId2"/>
     <sheet name="05,02" sheetId="118" r:id="rId3"/>
+    <sheet name="05,03" sheetId="119" r:id="rId4"/>
+    <sheet name="05,06" sheetId="120" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'05,02'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'05,03'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'05,06'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -295,8 +299,180 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{85DA0824-366C-4654-AB05-FB699122A6BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{6336451C-8DD0-4362-AE18-728A873BA8AA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{4B7C947E-1465-4BB2-8F41-A0370E3CB603}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{C5385E34-5830-4B3D-AA6C-66170F58928B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{8107B914-79D2-4CCE-B4E7-987A683B02FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{1686C1C6-4F46-4C74-B6A4-CB959556C4DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -1904,7 +2080,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2470,6 +2646,15 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="94" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2909,15 +3094,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
-      <c r="V1" s="195"/>
-      <c r="W1" s="195"/>
-      <c r="X1" s="196"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
+      <c r="V1" s="198"/>
+      <c r="W1" s="198"/>
+      <c r="X1" s="199"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -2942,62 +3127,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="197" t="s">
+      <c r="B4" s="200" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="C4" s="201" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="199" t="s">
+      <c r="D4" s="202" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="200" t="s">
+      <c r="E4" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="201"/>
-      <c r="G4" s="202" t="s">
+      <c r="F4" s="204"/>
+      <c r="G4" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="204" t="s">
+      <c r="H4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="206" t="s">
+      <c r="I4" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="204" t="s">
+      <c r="J4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="208" t="s">
+      <c r="L4" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="209"/>
-      <c r="N4" s="209"/>
-      <c r="O4" s="209"/>
-      <c r="P4" s="209"/>
-      <c r="Q4" s="209"/>
-      <c r="R4" s="209"/>
-      <c r="S4" s="209"/>
-      <c r="T4" s="209"/>
-      <c r="U4" s="209"/>
-      <c r="V4" s="210"/>
-      <c r="W4" s="209"/>
-      <c r="X4" s="211"/>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="212"/>
+      <c r="X4" s="214"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="197"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="199"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="202"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="203"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="205"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="208"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5248,7 +5433,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="189" t="s">
+      <c r="G62" s="192" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5266,7 +5451,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="190"/>
+      <c r="G63" s="193"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5282,7 +5467,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="191"/>
+      <c r="G64" s="194"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5298,7 +5483,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="192" t="s">
+      <c r="G65" s="195" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5316,7 +5501,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="192"/>
+      <c r="G66" s="195"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5332,7 +5517,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="193"/>
+      <c r="G67" s="196"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -5727,17 +5912,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="194">
+      <c r="P1" s="197">
         <v>46204</v>
       </c>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
-      <c r="V1" s="195"/>
-      <c r="W1" s="195"/>
-      <c r="X1" s="196"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
+      <c r="V1" s="198"/>
+      <c r="W1" s="198"/>
+      <c r="X1" s="199"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -5762,62 +5947,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="197" t="s">
+      <c r="B4" s="200" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="C4" s="201" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="199" t="s">
+      <c r="D4" s="202" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="200" t="s">
+      <c r="E4" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="201"/>
-      <c r="G4" s="202" t="s">
+      <c r="F4" s="204"/>
+      <c r="G4" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="204" t="s">
+      <c r="H4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="206" t="s">
+      <c r="I4" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="204" t="s">
+      <c r="J4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="208" t="s">
+      <c r="L4" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="209"/>
-      <c r="N4" s="209"/>
-      <c r="O4" s="209"/>
-      <c r="P4" s="209"/>
-      <c r="Q4" s="209"/>
-      <c r="R4" s="209"/>
-      <c r="S4" s="209"/>
-      <c r="T4" s="209"/>
-      <c r="U4" s="209"/>
-      <c r="V4" s="210"/>
-      <c r="W4" s="209"/>
-      <c r="X4" s="211"/>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="212"/>
+      <c r="X4" s="214"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="197"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="199"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="202"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="203"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="205"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="208"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9275,7 +9460,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="189" t="s">
+      <c r="G62" s="192" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9293,7 +9478,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="190"/>
+      <c r="G63" s="193"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9309,7 +9494,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="191"/>
+      <c r="G64" s="194"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9325,7 +9510,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="192" t="s">
+      <c r="G65" s="195" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9343,7 +9528,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="192"/>
+      <c r="G66" s="195"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9359,7 +9544,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="193"/>
+      <c r="G67" s="196"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -9754,17 +9939,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="194">
+      <c r="P1" s="197">
         <v>46205</v>
       </c>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
-      <c r="V1" s="195"/>
-      <c r="W1" s="195"/>
-      <c r="X1" s="196"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
+      <c r="V1" s="198"/>
+      <c r="W1" s="198"/>
+      <c r="X1" s="199"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9789,62 +9974,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="197" t="s">
+      <c r="B4" s="200" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="C4" s="201" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="199" t="s">
+      <c r="D4" s="202" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="200" t="s">
+      <c r="E4" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="201"/>
-      <c r="G4" s="202" t="s">
+      <c r="F4" s="204"/>
+      <c r="G4" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="204" t="s">
+      <c r="H4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="206" t="s">
+      <c r="I4" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="204" t="s">
+      <c r="J4" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="208" t="s">
+      <c r="L4" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="209"/>
-      <c r="N4" s="209"/>
-      <c r="O4" s="209"/>
-      <c r="P4" s="209"/>
-      <c r="Q4" s="209"/>
-      <c r="R4" s="209"/>
-      <c r="S4" s="209"/>
-      <c r="T4" s="209"/>
-      <c r="U4" s="209"/>
-      <c r="V4" s="210"/>
-      <c r="W4" s="209"/>
-      <c r="X4" s="211"/>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="212"/>
+      <c r="X4" s="214"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="197"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="199"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="202"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="203"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="205"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="208"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13314,7 +13499,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="189" t="s">
+      <c r="G62" s="192" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13332,7 +13517,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="190"/>
+      <c r="G63" s="193"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13348,7 +13533,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="191"/>
+      <c r="G64" s="194"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13364,7 +13549,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="192" t="s">
+      <c r="G65" s="195" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13382,7 +13567,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="192"/>
+      <c r="G66" s="195"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13398,7 +13583,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="193"/>
+      <c r="G67" s="196"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -13422,6 +13607,7970 @@
         <v>3</v>
       </c>
       <c r="D69" s="185"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B31D4DF-DEF4-46E2-B4E9-2D81C88F47C3}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="197">
+        <v>46206</v>
+      </c>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
+      <c r="V1" s="198"/>
+      <c r="W1" s="198"/>
+      <c r="X1" s="199"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="200" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="201" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="202" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="203" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="204"/>
+      <c r="G4" s="205" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="207" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="209" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="207" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="211" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="212"/>
+      <c r="X4" s="214"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="206"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="208"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>41</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>40</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112">
+        <v>1</v>
+      </c>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>1</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>24</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>1</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>969</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>109</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78">
+        <v>1</v>
+      </c>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>108</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121">
+        <v>1</v>
+      </c>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>24</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>1</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2592</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>154</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>154</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>3696</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>118</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>118</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>2832</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3949</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>27</v>
+      </c>
+      <c r="H13" s="79">
+        <v>24</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3922</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>-12</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>6</v>
+      </c>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
+      <c r="N13" s="121">
+        <v>8</v>
+      </c>
+      <c r="O13" s="121">
+        <v>12</v>
+      </c>
+      <c r="P13" s="121">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>27</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>24</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>648</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>94116</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>115</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>3</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>112</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>1</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>2689</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>137</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>11</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>126</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>264</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>3024</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>23</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>533</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>4</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>159</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>159</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>3830</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3915</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>92</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>3823</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>8</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>30</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>54</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>552</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>92</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>22939</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>118</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>3</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>115</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154">
+        <v>1</v>
+      </c>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>72</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>2780</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>49</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>48</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>16</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>2</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>30</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>576</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>48</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>12</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>50085</v>
+      </c>
+      <c r="D44" s="114">
+        <v>5</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>1192</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>48893</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>404</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>322</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>466</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>1192</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>7152</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>1192</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>293363</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>96</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2766</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>2766</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16597</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>61866</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>145</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1380</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>24</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>60486</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>121</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>438</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>363</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>579</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>1380</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>9432</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1380</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>452485</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="193"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="194"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="195" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="195"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="196"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="189" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="190"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EC531BF-A334-4202-BF36-08F18A917221}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="197">
+        <v>46209</v>
+      </c>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
+      <c r="V1" s="198"/>
+      <c r="W1" s="198"/>
+      <c r="X1" s="199"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="200" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="201" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="202" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="203" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="204"/>
+      <c r="G4" s="205" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="207" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="209" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="207" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="211" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="212"/>
+      <c r="X4" s="214"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="206"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="208"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146"/>
+      <c r="D41" s="147"/>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121"/>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>0</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>0</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>0</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>0</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141"/>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>0</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="193"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="194"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="195" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="195"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="196"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="189" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="190"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E212B63-5378-4505-AE18-5F9A2A0079EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B92126-3E26-4276-9869-638EADA8CA8F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18294,19 +18294,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>40</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -18334,7 +18338,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -18369,15 +18373,19 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>108</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
+      <c r="G9" s="78">
+        <v>1</v>
+      </c>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -18386,13 +18394,15 @@
       <c r="K9" s="51"/>
       <c r="L9" s="121"/>
       <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
+      <c r="N9" s="121">
+        <v>1</v>
+      </c>
       <c r="O9" s="121"/>
       <c r="P9" s="121"/>
       <c r="Q9" s="122"/>
       <c r="R9" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="125">
         <f t="shared" si="1"/>
@@ -18401,15 +18411,15 @@
       <c r="T9" s="51"/>
       <c r="U9" s="131">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V9" s="132">
         <f>U9/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -18444,22 +18454,28 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>154</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>1</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
+      <c r="L10" s="112">
+        <v>1</v>
+      </c>
       <c r="M10" s="112"/>
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
@@ -18467,7 +18483,7 @@
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -18476,15 +18492,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3672</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -18519,22 +18535,28 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>118</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>1</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="112"/>
+      <c r="L11" s="112">
+        <v>1</v>
+      </c>
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
@@ -18542,7 +18564,7 @@
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -18551,15 +18573,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2808</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -18594,19 +18616,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -18634,7 +18660,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -18669,47 +18695,63 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3921</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>29</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3892</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
         <v>0</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
+      <c r="L13" s="121">
+        <v>5</v>
+      </c>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121">
+        <v>12</v>
+      </c>
+      <c r="P13" s="121">
+        <v>14</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>93408</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -18751,19 +18793,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -18791,7 +18837,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -18826,7 +18872,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -18834,7 +18882,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -18866,7 +18914,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -19051,7 +19099,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -19059,7 +19109,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -19091,7 +19141,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -19201,19 +19251,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -19241,7 +19295,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -19276,7 +19330,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -19284,7 +19340,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -19316,7 +19372,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -19351,7 +19407,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -19359,7 +19417,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -19391,7 +19449,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -19427,7 +19485,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -19438,7 +19498,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -19466,7 +19526,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -19508,19 +19568,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -19548,7 +19612,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -19590,7 +19654,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -19598,7 +19664,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -19630,7 +19696,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -19665,30 +19731,40 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>112</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>7</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
-      <c r="L26" s="112"/>
+      <c r="L26" s="112">
+        <v>5</v>
+      </c>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="8"/>
@@ -19697,15 +19773,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2521</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -19780,7 +19856,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -19788,7 +19866,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -19820,7 +19898,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -19839,7 +19917,9 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>126</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
@@ -19847,7 +19927,7 @@
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
@@ -19879,7 +19959,7 @@
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -19898,19 +19978,23 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>22</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
       <c r="G30" s="76"/>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
@@ -19938,7 +20022,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>533</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -19950,7 +20034,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>3</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -19958,7 +20044,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -19990,7 +20076,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -20158,19 +20244,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>159</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -20198,7 +20288,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3830</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -20314,30 +20404,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3823</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>48</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3775</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>3</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>25</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>20</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -20346,15 +20448,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>22651</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -20470,19 +20572,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>115</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -20510,7 +20616,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2780</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -20522,7 +20628,9 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>1</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
@@ -20530,7 +20638,7 @@
       <c r="H42" s="167"/>
       <c r="I42" s="187">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
@@ -20562,7 +20670,7 @@
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -20617,30 +20725,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>48893</v>
+      </c>
+      <c r="D44" s="114">
+        <v>5</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>965</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="188">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47928</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>293</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>306</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>366</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -20649,15 +20769,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5790</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>287573</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -20765,7 +20885,9 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="110"/>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
       <c r="D47" s="111"/>
       <c r="E47" s="112"/>
       <c r="F47" s="112"/>
@@ -20773,7 +20895,7 @@
       <c r="H47" s="73"/>
       <c r="I47" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="77">
         <f t="shared" si="7"/>
@@ -20805,7 +20927,7 @@
       </c>
       <c r="W47" s="129">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X47" s="27"/>
     </row>
@@ -20817,19 +20939,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2766</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2766</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -20857,7 +20983,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16597</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -20869,7 +20995,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -20877,7 +21005,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -20909,7 +21037,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -21025,7 +21153,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -21033,7 +21163,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -21065,7 +21195,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -21129,7 +21259,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -21137,7 +21269,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -21169,7 +21301,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -21384,11 +21516,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>60485</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -21397,24 +21529,24 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>59433</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
@@ -21422,15 +21554,15 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
@@ -21438,24 +21570,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>7014</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="W60" s="183">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>445459</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B92126-3E26-4276-9869-638EADA8CA8F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACFCB7E-44A4-437A-AFCD-A07C5DFB5D43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACFCB7E-44A4-437A-AFCD-A07C5DFB5D43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5DE56C-A6C9-4B79-9A14-668F6CBA3B2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -18,12 +18,14 @@
     <sheet name="05,02" sheetId="118" r:id="rId3"/>
     <sheet name="05,03" sheetId="119" r:id="rId4"/>
     <sheet name="05,06" sheetId="120" r:id="rId5"/>
+    <sheet name="05,07" sheetId="121" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'05,02'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'05,03'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05,06'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'05,07'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -471,8 +473,94 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{AFE0FD1D-82F0-436D-98DE-709063B2C281}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{B5A2B953-CBA9-4273-8FB4-17D139B72536}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{36EBA229-077A-445F-9903-6A6A026C1741}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2080,7 +2168,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2655,6 +2743,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3094,15 +3191,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="198"/>
-      <c r="U1" s="198"/>
-      <c r="V1" s="198"/>
-      <c r="W1" s="198"/>
-      <c r="X1" s="199"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="201"/>
+      <c r="S1" s="201"/>
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="201"/>
+      <c r="W1" s="201"/>
+      <c r="X1" s="202"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3127,62 +3224,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205" t="s">
+      <c r="F4" s="207"/>
+      <c r="G4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="209" t="s">
+      <c r="I4" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="211" t="s">
+      <c r="L4" s="214" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="212"/>
-      <c r="N4" s="212"/>
-      <c r="O4" s="212"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="212"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="212"/>
-      <c r="T4" s="212"/>
-      <c r="U4" s="212"/>
-      <c r="V4" s="213"/>
-      <c r="W4" s="212"/>
-      <c r="X4" s="214"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="217"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="202"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="205"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="206"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5433,7 +5530,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="192" t="s">
+      <c r="G62" s="195" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5451,7 +5548,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="193"/>
+      <c r="G63" s="196"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5467,7 +5564,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="194"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5483,7 +5580,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="195" t="s">
+      <c r="G65" s="198" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5501,7 +5598,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="195"/>
+      <c r="G66" s="198"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5517,7 +5614,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="196"/>
+      <c r="G67" s="199"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -5912,17 +6009,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="197">
+      <c r="P1" s="200">
         <v>46204</v>
       </c>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="198"/>
-      <c r="U1" s="198"/>
-      <c r="V1" s="198"/>
-      <c r="W1" s="198"/>
-      <c r="X1" s="199"/>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="201"/>
+      <c r="S1" s="201"/>
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="201"/>
+      <c r="W1" s="201"/>
+      <c r="X1" s="202"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -5947,62 +6044,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205" t="s">
+      <c r="F4" s="207"/>
+      <c r="G4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="209" t="s">
+      <c r="I4" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="211" t="s">
+      <c r="L4" s="214" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="212"/>
-      <c r="N4" s="212"/>
-      <c r="O4" s="212"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="212"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="212"/>
-      <c r="T4" s="212"/>
-      <c r="U4" s="212"/>
-      <c r="V4" s="213"/>
-      <c r="W4" s="212"/>
-      <c r="X4" s="214"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="217"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="202"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="205"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="206"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9460,7 +9557,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="192" t="s">
+      <c r="G62" s="195" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9478,7 +9575,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="193"/>
+      <c r="G63" s="196"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9494,7 +9591,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="194"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9510,7 +9607,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="195" t="s">
+      <c r="G65" s="198" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9528,7 +9625,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="195"/>
+      <c r="G66" s="198"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9544,7 +9641,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="196"/>
+      <c r="G67" s="199"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -9939,17 +10036,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="197">
+      <c r="P1" s="200">
         <v>46205</v>
       </c>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="198"/>
-      <c r="U1" s="198"/>
-      <c r="V1" s="198"/>
-      <c r="W1" s="198"/>
-      <c r="X1" s="199"/>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="201"/>
+      <c r="S1" s="201"/>
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="201"/>
+      <c r="W1" s="201"/>
+      <c r="X1" s="202"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -9974,62 +10071,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205" t="s">
+      <c r="F4" s="207"/>
+      <c r="G4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="209" t="s">
+      <c r="I4" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="211" t="s">
+      <c r="L4" s="214" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="212"/>
-      <c r="N4" s="212"/>
-      <c r="O4" s="212"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="212"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="212"/>
-      <c r="T4" s="212"/>
-      <c r="U4" s="212"/>
-      <c r="V4" s="213"/>
-      <c r="W4" s="212"/>
-      <c r="X4" s="214"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="217"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="202"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="205"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="206"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13499,7 +13596,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="192" t="s">
+      <c r="G62" s="195" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13517,7 +13614,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="193"/>
+      <c r="G63" s="196"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13533,7 +13630,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="194"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13549,7 +13646,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="195" t="s">
+      <c r="G65" s="198" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13567,7 +13664,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="195"/>
+      <c r="G66" s="198"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13583,7 +13680,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="196"/>
+      <c r="G67" s="199"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -13978,17 +14075,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="197">
+      <c r="P1" s="200">
         <v>46206</v>
       </c>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="198"/>
-      <c r="U1" s="198"/>
-      <c r="V1" s="198"/>
-      <c r="W1" s="198"/>
-      <c r="X1" s="199"/>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="201"/>
+      <c r="S1" s="201"/>
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="201"/>
+      <c r="W1" s="201"/>
+      <c r="X1" s="202"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14013,62 +14110,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205" t="s">
+      <c r="F4" s="207"/>
+      <c r="G4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="209" t="s">
+      <c r="I4" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="211" t="s">
+      <c r="L4" s="214" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="212"/>
-      <c r="N4" s="212"/>
-      <c r="O4" s="212"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="212"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="212"/>
-      <c r="T4" s="212"/>
-      <c r="U4" s="212"/>
-      <c r="V4" s="213"/>
-      <c r="W4" s="212"/>
-      <c r="X4" s="214"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="217"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="202"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="205"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="206"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17560,7 +17657,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="192" t="s">
+      <c r="G62" s="195" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17578,7 +17675,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="193"/>
+      <c r="G63" s="196"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17594,7 +17691,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="194"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17610,7 +17707,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="195" t="s">
+      <c r="G65" s="198" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17628,7 +17725,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="195"/>
+      <c r="G66" s="198"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17644,7 +17741,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="196"/>
+      <c r="G67" s="199"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18039,17 +18136,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="197">
+      <c r="P1" s="200">
         <v>46209</v>
       </c>
-      <c r="Q1" s="198"/>
-      <c r="R1" s="198"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="198"/>
-      <c r="U1" s="198"/>
-      <c r="V1" s="198"/>
-      <c r="W1" s="198"/>
-      <c r="X1" s="199"/>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="201"/>
+      <c r="S1" s="201"/>
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="201"/>
+      <c r="W1" s="201"/>
+      <c r="X1" s="202"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18074,62 +18171,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="203" t="s">
+      <c r="E4" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="204"/>
-      <c r="G4" s="205" t="s">
+      <c r="F4" s="207"/>
+      <c r="G4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="209" t="s">
+      <c r="I4" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="211" t="s">
+      <c r="L4" s="214" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="212"/>
-      <c r="N4" s="212"/>
-      <c r="O4" s="212"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="212"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="212"/>
-      <c r="T4" s="212"/>
-      <c r="U4" s="212"/>
-      <c r="V4" s="213"/>
-      <c r="W4" s="212"/>
-      <c r="X4" s="214"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="217"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="202"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="205"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="206"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21595,7 +21692,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="192" t="s">
+      <c r="G62" s="195" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21613,7 +21710,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="193"/>
+      <c r="G63" s="196"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21629,7 +21726,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="194"/>
+      <c r="G64" s="197"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -21645,7 +21742,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="195" t="s">
+      <c r="G65" s="198" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -21663,7 +21760,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="195"/>
+      <c r="G66" s="198"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -21679,7 +21776,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="196"/>
+      <c r="G67" s="199"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -21703,6 +21800,4029 @@
         <v>3</v>
       </c>
       <c r="D69" s="190"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFAA1CB-968C-45B2-AD11-43C7C80C35C5}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="200">
+        <v>46210</v>
+      </c>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="201"/>
+      <c r="S1" s="201"/>
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="201"/>
+      <c r="W1" s="201"/>
+      <c r="X1" s="202"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="203" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="204" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="205" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="206" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="207"/>
+      <c r="G4" s="208" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="210" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="212" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="210" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="214" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="216"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="217"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="194" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="209"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="211"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>40</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>40</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>969</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>107</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>107</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2568</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>153</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>153</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>3672</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>117</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>117</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>2808</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3892</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>33</v>
+      </c>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3859</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>12</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121">
+        <v>12</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>33</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>792</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>92616</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>105</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>105</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>2521</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>126</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>4</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>122</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>96</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>2928</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>22</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>533</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>3</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>159</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>2</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>3782</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3775</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>170</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>3605</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>11</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>70</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>89</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>170</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>1020</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>170</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>21631</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>115</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>115</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>2780</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>1</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>1</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>12</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>1</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>47928</v>
+      </c>
+      <c r="D44" s="114">
+        <v>5</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>959</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>46969</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>324</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>356</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>279</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>959</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>5754</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>959</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>281819</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>96</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2766</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>2766</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16597</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>59433</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>133</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1169</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>58264</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>133</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>347</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>438</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>384</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>1169</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>7722</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1169</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>437737</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="195" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="196"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="197"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="198" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="198"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="199"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="192" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="193"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5DE56C-A6C9-4B79-9A14-668F6CBA3B2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F51EC12-1352-44DD-AD24-229F9516F49C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="05,03" sheetId="119" r:id="rId4"/>
     <sheet name="05,06" sheetId="120" r:id="rId5"/>
     <sheet name="05,07" sheetId="121" r:id="rId6"/>
+    <sheet name="05,08" sheetId="122" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -26,6 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'05,03'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05,06'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'05,07'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'05,08'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -559,8 +561,94 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{A56D6E7B-761B-4E9D-951F-E9F826B43225}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{1143076B-EE2F-4D5E-8C23-1C1C4F7141DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{66C7F473-61E4-4352-A6AB-B682A595D79D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2168,7 +2256,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2752,6 +2840,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3191,15 +3288,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="P1" s="203"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3224,62 +3321,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5530,7 +5627,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5548,7 +5645,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5564,7 +5661,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5580,7 +5677,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5598,7 +5695,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5614,7 +5711,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6009,17 +6106,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46204</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6044,62 +6141,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9557,7 +9654,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9575,7 +9672,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9591,7 +9688,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9607,7 +9704,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9625,7 +9722,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9641,7 +9738,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10036,17 +10133,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46205</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10071,62 +10168,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13596,7 +13693,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13614,7 +13711,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13630,7 +13727,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13646,7 +13743,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13664,7 +13761,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13680,7 +13777,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14075,17 +14172,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46206</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14110,62 +14207,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17657,7 +17754,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17675,7 +17772,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17691,7 +17788,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17707,7 +17804,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17725,7 +17822,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17741,7 +17838,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18136,17 +18233,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46209</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18171,62 +18268,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21692,7 +21789,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21710,7 +21807,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21726,7 +21823,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -21742,7 +21839,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -21760,7 +21857,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -21776,7 +21873,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22171,17 +22268,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200">
+      <c r="P1" s="203">
         <v>46210</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="202"/>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22206,62 +22303,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="206" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="204" t="s">
+      <c r="C4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208" t="s">
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="210" t="s">
+      <c r="J4" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="214" t="s">
+      <c r="L4" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="215"/>
-      <c r="N4" s="215"/>
-      <c r="O4" s="215"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="215"/>
-      <c r="T4" s="215"/>
-      <c r="U4" s="215"/>
-      <c r="V4" s="216"/>
-      <c r="W4" s="215"/>
-      <c r="X4" s="217"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="209"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="211"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25715,7 +25812,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="195" t="s">
+      <c r="G62" s="198" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -25733,7 +25830,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="196"/>
+      <c r="G63" s="199"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -25749,7 +25846,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="197"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -25765,7 +25862,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="198" t="s">
+      <c r="G65" s="201" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -25783,7 +25880,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="198"/>
+      <c r="G66" s="201"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -25799,7 +25896,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="199"/>
+      <c r="G67" s="202"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -25823,6 +25920,4045 @@
         <v>3</v>
       </c>
       <c r="D69" s="193"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9539F20-70E0-4F2D-9828-9BD8834E8F79}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="203">
+        <v>46211</v>
+      </c>
+      <c r="Q1" s="204"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="204"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="205"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="206" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="207" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="208" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="209" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="210"/>
+      <c r="G4" s="211" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="213" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="215" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="213" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="217" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="218"/>
+      <c r="Q4" s="218"/>
+      <c r="R4" s="218"/>
+      <c r="S4" s="218"/>
+      <c r="T4" s="218"/>
+      <c r="U4" s="218"/>
+      <c r="V4" s="219"/>
+      <c r="W4" s="218"/>
+      <c r="X4" s="220"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="197" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="212"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>40</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>40</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>969</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>107</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>107</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2568</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>153</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>15</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>138</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>360</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>15</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>3312</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>117</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76">
+        <v>17</v>
+      </c>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>408</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>17</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>2400</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3859</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>20</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3839</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>-12</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
+      <c r="N13" s="121">
+        <v>8</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>20</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>12</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>480</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>92124</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>105</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>105</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>2521</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>122</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>1</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>121</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>2904</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>22</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>1</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112">
+        <v>1</v>
+      </c>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>509</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>3</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>157</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>6</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>151</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112">
+        <v>5</v>
+      </c>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112">
+        <v>1</v>
+      </c>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>144</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>3638</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3605</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>101</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>3504</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>20</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>26</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>55</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>101</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>606</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>101</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>21025</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>115</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>46</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>69</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154">
+        <v>45</v>
+      </c>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154">
+        <v>1</v>
+      </c>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>46</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>1104</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>46</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>1676</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>46969</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>917</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>46052</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>289</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>254</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>374</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>917</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>5502</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>917</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>276315</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>96</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2766</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>2766</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16597</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>58264</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>131</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1124</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>12</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>57140</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>119</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>360</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>291</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>473</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>1124</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>8652</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1124</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>429071</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="198" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="199"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="200"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="201" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="201"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="202"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="195" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="196"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F51EC12-1352-44DD-AD24-229F9516F49C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833BDDB7-43C4-4296-9072-D33A9EE4B4F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="05,06" sheetId="120" r:id="rId5"/>
     <sheet name="05,07" sheetId="121" r:id="rId6"/>
     <sheet name="05,08" sheetId="122" r:id="rId7"/>
+    <sheet name="05,09" sheetId="123" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -28,6 +29,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'05,06'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'05,07'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'05,08'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'05,09'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -647,8 +649,94 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{05862FB6-0215-4E75-B5C3-454C2C5BA9F9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{86475769-63CB-4ECE-BC3E-62FEB140C8B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{FEBACCBB-B028-41D7-AB1B-BB4A90A2EAB8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2256,7 +2344,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2849,6 +2937,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3288,15 +3385,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="205"/>
+      <c r="P1" s="206"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3321,62 +3418,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="211" t="s">
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="217" t="s">
+      <c r="L4" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="218"/>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="218"/>
-      <c r="S4" s="218"/>
-      <c r="T4" s="218"/>
-      <c r="U4" s="218"/>
-      <c r="V4" s="219"/>
-      <c r="W4" s="218"/>
-      <c r="X4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="214"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5627,7 +5724,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="198" t="s">
+      <c r="G62" s="201" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5645,7 +5742,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="199"/>
+      <c r="G63" s="202"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5661,7 +5758,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="200"/>
+      <c r="G64" s="203"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5677,7 +5774,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="201" t="s">
+      <c r="G65" s="204" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5695,7 +5792,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="201"/>
+      <c r="G66" s="204"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5711,7 +5808,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="202"/>
+      <c r="G67" s="205"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6106,17 +6203,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="203">
+      <c r="P1" s="206">
         <v>46204</v>
       </c>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="205"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6141,62 +6238,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="211" t="s">
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="217" t="s">
+      <c r="L4" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="218"/>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="218"/>
-      <c r="S4" s="218"/>
-      <c r="T4" s="218"/>
-      <c r="U4" s="218"/>
-      <c r="V4" s="219"/>
-      <c r="W4" s="218"/>
-      <c r="X4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="214"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9654,7 +9751,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="198" t="s">
+      <c r="G62" s="201" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9672,7 +9769,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="199"/>
+      <c r="G63" s="202"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9688,7 +9785,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="200"/>
+      <c r="G64" s="203"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9704,7 +9801,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="201" t="s">
+      <c r="G65" s="204" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9722,7 +9819,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="201"/>
+      <c r="G66" s="204"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9738,7 +9835,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="202"/>
+      <c r="G67" s="205"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10133,17 +10230,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="203">
+      <c r="P1" s="206">
         <v>46205</v>
       </c>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="205"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10168,62 +10265,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="211" t="s">
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="217" t="s">
+      <c r="L4" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="218"/>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="218"/>
-      <c r="S4" s="218"/>
-      <c r="T4" s="218"/>
-      <c r="U4" s="218"/>
-      <c r="V4" s="219"/>
-      <c r="W4" s="218"/>
-      <c r="X4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="214"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13693,7 +13790,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="198" t="s">
+      <c r="G62" s="201" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13711,7 +13808,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="199"/>
+      <c r="G63" s="202"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13727,7 +13824,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="200"/>
+      <c r="G64" s="203"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13743,7 +13840,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="201" t="s">
+      <c r="G65" s="204" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13761,7 +13858,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="201"/>
+      <c r="G66" s="204"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13777,7 +13874,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="202"/>
+      <c r="G67" s="205"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14172,17 +14269,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="203">
+      <c r="P1" s="206">
         <v>46206</v>
       </c>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="205"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14207,62 +14304,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="211" t="s">
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="217" t="s">
+      <c r="L4" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="218"/>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="218"/>
-      <c r="S4" s="218"/>
-      <c r="T4" s="218"/>
-      <c r="U4" s="218"/>
-      <c r="V4" s="219"/>
-      <c r="W4" s="218"/>
-      <c r="X4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="214"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17754,7 +17851,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="198" t="s">
+      <c r="G62" s="201" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17772,7 +17869,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="199"/>
+      <c r="G63" s="202"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17788,7 +17885,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="200"/>
+      <c r="G64" s="203"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17804,7 +17901,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="201" t="s">
+      <c r="G65" s="204" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17822,7 +17919,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="201"/>
+      <c r="G66" s="204"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17838,7 +17935,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="202"/>
+      <c r="G67" s="205"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18233,17 +18330,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="203">
+      <c r="P1" s="206">
         <v>46209</v>
       </c>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="205"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18268,62 +18365,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="211" t="s">
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="217" t="s">
+      <c r="L4" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="218"/>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="218"/>
-      <c r="S4" s="218"/>
-      <c r="T4" s="218"/>
-      <c r="U4" s="218"/>
-      <c r="V4" s="219"/>
-      <c r="W4" s="218"/>
-      <c r="X4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="214"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21789,7 +21886,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="198" t="s">
+      <c r="G62" s="201" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21807,7 +21904,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="199"/>
+      <c r="G63" s="202"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21823,7 +21920,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="200"/>
+      <c r="G64" s="203"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -21839,7 +21936,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="201" t="s">
+      <c r="G65" s="204" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -21857,7 +21954,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="201"/>
+      <c r="G66" s="204"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -21873,7 +21970,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="202"/>
+      <c r="G67" s="205"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22268,17 +22365,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="203">
+      <c r="P1" s="206">
         <v>46210</v>
       </c>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="205"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22303,62 +22400,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="211" t="s">
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="217" t="s">
+      <c r="L4" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="218"/>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="218"/>
-      <c r="S4" s="218"/>
-      <c r="T4" s="218"/>
-      <c r="U4" s="218"/>
-      <c r="V4" s="219"/>
-      <c r="W4" s="218"/>
-      <c r="X4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="214"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25812,7 +25909,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="198" t="s">
+      <c r="G62" s="201" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -25830,7 +25927,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="199"/>
+      <c r="G63" s="202"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -25846,7 +25943,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="200"/>
+      <c r="G64" s="203"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -25862,7 +25959,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="201" t="s">
+      <c r="G65" s="204" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -25880,7 +25977,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="201"/>
+      <c r="G66" s="204"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -25896,7 +25993,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="202"/>
+      <c r="G67" s="205"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26291,17 +26388,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="203">
+      <c r="P1" s="206">
         <v>46211</v>
       </c>
-      <c r="Q1" s="204"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204"/>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-      <c r="X1" s="205"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26326,62 +26423,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="211" t="s">
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="213" t="s">
+      <c r="H4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="215" t="s">
+      <c r="I4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="213" t="s">
+      <c r="J4" s="216" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="217" t="s">
+      <c r="L4" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="218"/>
-      <c r="Q4" s="218"/>
-      <c r="R4" s="218"/>
-      <c r="S4" s="218"/>
-      <c r="T4" s="218"/>
-      <c r="U4" s="218"/>
-      <c r="V4" s="219"/>
-      <c r="W4" s="218"/>
-      <c r="X4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="207"/>
-      <c r="D5" s="208"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="197" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="214"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -29851,7 +29948,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="198" t="s">
+      <c r="G62" s="201" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -29869,7 +29966,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="199"/>
+      <c r="G63" s="202"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -29885,7 +29982,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="200"/>
+      <c r="G64" s="203"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -29901,7 +29998,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="201" t="s">
+      <c r="G65" s="204" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -29919,7 +30016,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="201"/>
+      <c r="G66" s="204"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -29935,7 +30032,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="202"/>
+      <c r="G67" s="205"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -29959,6 +30056,4053 @@
         <v>3</v>
       </c>
       <c r="D69" s="196"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EEE0EB-F7F3-4644-B487-D03D204F5D24}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="206">
+        <v>46211</v>
+      </c>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="208"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="209" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="210" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="211" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="212" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="213"/>
+      <c r="G4" s="214" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="216" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="218" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="216" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="220" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="222"/>
+      <c r="W4" s="221"/>
+      <c r="X4" s="223"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="200" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="215"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="217"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>40</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>40</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>969</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>107</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>107</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2568</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>138</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76">
+        <v>3</v>
+      </c>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112">
+        <v>1</v>
+      </c>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112">
+        <v>2</v>
+      </c>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>72</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>3</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>3240</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>100</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76">
+        <v>1</v>
+      </c>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>99</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112">
+        <v>1</v>
+      </c>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>24</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>1</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>2376</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3838</v>
+      </c>
+      <c r="D13" s="114">
+        <v>12</v>
+      </c>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>23</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3815</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121">
+        <v>10</v>
+      </c>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121">
+        <v>10</v>
+      </c>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>23</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>12</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>552</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>91560</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>105</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>1</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>1</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>2497</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>121</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>7</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>114</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112">
+        <v>1</v>
+      </c>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112">
+        <v>2</v>
+      </c>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>168</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>2736</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>21</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>509</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>3</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>151</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112">
+        <v>1</v>
+      </c>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>3614</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3504</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>39</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>3465</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>20</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>10</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>9</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>39</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>234</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>39</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>20791</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>69</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>69</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>1676</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>46052</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>781</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>45271</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>356</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>292</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>133</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>781</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>4686</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>781</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>271629</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>96</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2766</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143">
+        <v>4</v>
+      </c>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>2762</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121">
+        <v>3</v>
+      </c>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121">
+        <v>1</v>
+      </c>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>24</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>4</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16573</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>57139</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>143</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>860</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>12</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>56279</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>131</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>394</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>317</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>149</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>860</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>5808</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>860</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>423251</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="201" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="202"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="203"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="204" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="204"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="205"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="198" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="199"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833BDDB7-43C4-4296-9072-D33A9EE4B4F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585F5FAE-DC71-4100-8574-8D9C354FC76D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="05,07" sheetId="121" r:id="rId6"/>
     <sheet name="05,08" sheetId="122" r:id="rId7"/>
     <sheet name="05,09" sheetId="123" r:id="rId8"/>
+    <sheet name="05,10" sheetId="124" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -30,6 +31,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'05,07'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'05,08'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'05,09'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'05,10'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -735,8 +737,94 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{3D7154B6-16A5-4ECD-B797-31DA15B89249}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{8A263F78-11F3-4E0F-99B6-576394703D5F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{0D4C13A9-01CB-42D4-B87E-B465C3798E1E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2344,7 +2432,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2946,6 +3034,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3385,15 +3482,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206"/>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="P1" s="209"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3418,62 +3515,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5724,7 +5821,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5742,7 +5839,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5758,7 +5855,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5774,7 +5871,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5792,7 +5889,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5808,7 +5905,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6203,17 +6300,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206">
+      <c r="P1" s="209">
         <v>46204</v>
       </c>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6238,62 +6335,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9751,7 +9848,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9769,7 +9866,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9785,7 +9882,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9801,7 +9898,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9819,7 +9916,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9835,7 +9932,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10230,17 +10327,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206">
+      <c r="P1" s="209">
         <v>46205</v>
       </c>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10265,62 +10362,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13790,7 +13887,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13808,7 +13905,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13824,7 +13921,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13840,7 +13937,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13858,7 +13955,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13874,7 +13971,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14269,17 +14366,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206">
+      <c r="P1" s="209">
         <v>46206</v>
       </c>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14304,62 +14401,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17851,7 +17948,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17869,7 +17966,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17885,7 +17982,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17901,7 +17998,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17919,7 +18016,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17935,7 +18032,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18330,17 +18427,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206">
+      <c r="P1" s="209">
         <v>46209</v>
       </c>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18365,62 +18462,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21886,7 +21983,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21904,7 +22001,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21920,7 +22017,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -21936,7 +22033,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -21954,7 +22051,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -21970,7 +22067,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22365,17 +22462,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206">
+      <c r="P1" s="209">
         <v>46210</v>
       </c>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22400,62 +22497,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25909,7 +26006,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -25927,7 +26024,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -25943,7 +26040,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -25959,7 +26056,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -25977,7 +26074,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -25993,7 +26090,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26388,17 +26485,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206">
+      <c r="P1" s="209">
         <v>46211</v>
       </c>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26423,62 +26520,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="197" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -29948,7 +30045,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -29966,7 +30063,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -29982,7 +30079,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -29998,7 +30095,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30016,7 +30113,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30032,7 +30129,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30427,17 +30524,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="206">
+      <c r="P1" s="209">
         <v>46211</v>
       </c>
-      <c r="Q1" s="207"/>
-      <c r="R1" s="207"/>
-      <c r="S1" s="207"/>
-      <c r="T1" s="207"/>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
-      <c r="W1" s="207"/>
-      <c r="X1" s="208"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30462,62 +30559,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="211" t="s">
+      <c r="D4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="212" t="s">
+      <c r="E4" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214" t="s">
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="216" t="s">
+      <c r="H4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="218" t="s">
+      <c r="I4" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="216" t="s">
+      <c r="J4" s="219" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="220" t="s">
+      <c r="L4" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-      <c r="U4" s="221"/>
-      <c r="V4" s="222"/>
-      <c r="W4" s="221"/>
-      <c r="X4" s="223"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="211"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="200" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="217"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="217"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -33995,7 +34092,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="201" t="s">
+      <c r="G62" s="204" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34013,7 +34110,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="202"/>
+      <c r="G63" s="205"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34029,7 +34126,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="203"/>
+      <c r="G64" s="206"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34045,7 +34142,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="204" t="s">
+      <c r="G65" s="207" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34063,7 +34160,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="204"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34079,7 +34176,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="205"/>
+      <c r="G67" s="208"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34103,6 +34200,4023 @@
         <v>3</v>
       </c>
       <c r="D69" s="199"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{223D3E97-D2BC-4541-9F55-DF2F2A0E42F8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="209">
+        <v>46213</v>
+      </c>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="210"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
+      <c r="W1" s="210"/>
+      <c r="X1" s="211"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="212" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="213" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="214" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="215" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="216"/>
+      <c r="G4" s="217" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="219" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="221" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="219" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="223" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="225"/>
+      <c r="W4" s="224"/>
+      <c r="X4" s="226"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="203" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="218"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="220"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110">
+        <v>40</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>40</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>969</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113">
+        <v>107</v>
+      </c>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78">
+        <v>1</v>
+      </c>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>106</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>24</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>1</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>2544</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110">
+        <v>135</v>
+      </c>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>3240</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110">
+        <v>99</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>99</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>2376</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113">
+        <v>3815</v>
+      </c>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78">
+        <v>4</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>3811</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>-12</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>4</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>12</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>96</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>91452</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>16</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>64</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>92</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>120</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>907</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>192</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110">
+        <v>104</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>2497</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>48</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110">
+        <v>114</v>
+      </c>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76">
+        <v>1</v>
+      </c>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>113</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>2712</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>21</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>509</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>3</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>72</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>150</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>149</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>3590</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3465</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>46</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>3419</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>46</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>46</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>276</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>46</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>20515</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>69</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149">
+        <v>2</v>
+      </c>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>67</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>1628</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>45271</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>276</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>44995</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>276</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>276</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>1656</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>276</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>269973</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>96</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2762</v>
+      </c>
+      <c r="D48" s="142">
+        <v>1</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>2762</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16573</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>56279</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>131</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>331</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>12</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>55948</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>119</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>331</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>331</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>2148</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>331</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>421091</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="204" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="205"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="206"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="207" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="207"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="208"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="201" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="202"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A857BCCC-31D2-47FE-B282-8C59512DFF50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C37B6FA-DC67-4305-8FFF-D6E6784C17BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="05,13" sheetId="126" r:id="rId11"/>
     <sheet name="05,14" sheetId="127" r:id="rId12"/>
     <sheet name="05,15" sheetId="128" r:id="rId13"/>
+    <sheet name="05,16" sheetId="129" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -40,6 +41,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'05,13'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'05,14'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'05,15'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'05,16'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -459,6 +461,92 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{8BE8558D-5F1B-4C3E-93DD-F0E640FDAC4B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{2EFBECB2-5C28-431F-ABF8-6E5392D09E28}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{47237E1D-7455-43F7-90E3-3927C5D21B64}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{101C32FA-C9DE-4C13-A2D6-3D18A72467F8}">
       <text>
         <r>
           <rPr>
@@ -1176,7 +1264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2784,7 +2872,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3404,6 +3492,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3843,15 +3940,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3876,62 +3973,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6182,7 +6279,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -6200,7 +6297,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -6216,7 +6313,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -6232,7 +6329,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -6250,7 +6347,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -6266,7 +6363,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6661,17 +6758,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46214</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6696,62 +6793,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -10199,7 +10296,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -10217,7 +10314,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -10233,7 +10330,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -10249,7 +10346,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -10267,7 +10364,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -10283,7 +10380,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10678,17 +10775,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46216</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10713,62 +10810,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14244,7 +14341,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -14262,7 +14359,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -14278,7 +14375,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -14294,7 +14391,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -14312,7 +14409,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -14328,7 +14425,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14723,17 +14820,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46217</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14758,62 +14855,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14978,19 +15075,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>40</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -15018,7 +15119,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -15053,22 +15154,28 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>106</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
+      <c r="G9" s="78">
+        <v>3</v>
+      </c>
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="51"/>
-      <c r="L9" s="121"/>
+      <c r="L9" s="121">
+        <v>3</v>
+      </c>
       <c r="M9" s="121"/>
       <c r="N9" s="121"/>
       <c r="O9" s="121"/>
@@ -15076,7 +15183,7 @@
       <c r="Q9" s="122"/>
       <c r="R9" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" s="125">
         <f t="shared" si="1"/>
@@ -15085,15 +15192,15 @@
       <c r="T9" s="51"/>
       <c r="U9" s="131">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V9" s="132">
         <f>U9/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -15128,15 +15235,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>131</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>2</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -15145,13 +15256,15 @@
       <c r="K10" s="41"/>
       <c r="L10" s="112"/>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>2</v>
+      </c>
       <c r="O10" s="112"/>
       <c r="P10" s="112"/>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -15160,15 +15273,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3096</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -15203,15 +15316,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>96</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>1</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -15220,13 +15337,15 @@
       <c r="K11" s="41"/>
       <c r="L11" s="112"/>
       <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
+      <c r="N11" s="112">
+        <v>1</v>
+      </c>
       <c r="O11" s="112"/>
       <c r="P11" s="112"/>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -15235,15 +15354,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -15278,19 +15397,23 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
       <c r="G12" s="76"/>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
@@ -15318,7 +15441,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -15353,47 +15476,59 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3752</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>18</v>
+      </c>
+      <c r="H13" s="79">
+        <v>12</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3734</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
+      <c r="L13" s="121">
+        <v>2</v>
+      </c>
+      <c r="M13" s="121">
+        <v>12</v>
+      </c>
       <c r="N13" s="121"/>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="P13" s="121">
+        <v>16</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>89604</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -15435,19 +15570,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -15475,7 +15614,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -15510,7 +15649,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -15518,7 +15659,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -15550,7 +15691,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -15735,7 +15876,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -15743,7 +15886,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -15775,7 +15918,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -15885,19 +16028,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -15925,7 +16072,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -15960,7 +16107,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -15968,7 +16117,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -16000,7 +16149,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -16035,7 +16184,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -16043,7 +16194,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -16075,7 +16226,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -16111,7 +16262,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -16122,7 +16275,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -16150,7 +16303,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -16192,19 +16345,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -16232,7 +16389,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -16274,7 +16431,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -16282,7 +16441,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
@@ -16314,7 +16473,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -16349,22 +16508,30 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>101</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>5</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
-      <c r="L26" s="112"/>
+      <c r="L26" s="112">
+        <v>5</v>
+      </c>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
@@ -16372,7 +16539,7 @@
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="8"/>
@@ -16381,15 +16548,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2305</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -16464,7 +16631,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -16472,7 +16641,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="7"/>
@@ -16504,7 +16673,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -16523,30 +16692,38 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>109</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>2</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
+      <c r="L29" s="112">
+        <v>1</v>
+      </c>
       <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
       <c r="O29" s="112"/>
       <c r="P29" s="112"/>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -16555,15 +16732,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2568</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -16582,22 +16759,30 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>20</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>3</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
-      <c r="L30" s="112"/>
+      <c r="L30" s="112">
+        <v>3</v>
+      </c>
       <c r="M30" s="112"/>
       <c r="N30" s="112"/>
       <c r="O30" s="112"/>
@@ -16605,7 +16790,7 @@
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -16614,15 +16799,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -16634,22 +16819,28 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>3</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>2</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K31" s="41"/>
-      <c r="L31" s="112"/>
+      <c r="L31" s="112">
+        <v>2</v>
+      </c>
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
@@ -16657,7 +16848,7 @@
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="8"/>
@@ -16666,15 +16857,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -16842,19 +17033,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>139</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -16882,7 +17077,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3350</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -16998,30 +17193,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3242</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>112</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3130</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>18</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>22</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>72</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -17030,15 +17237,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>18781</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -17154,22 +17361,30 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>67</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>55</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
-      <c r="L41" s="154"/>
+      <c r="L41" s="154">
+        <v>55</v>
+      </c>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
@@ -17177,7 +17392,7 @@
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="8"/>
@@ -17186,15 +17401,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -17301,30 +17516,42 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>43049</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>731</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="188">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42318</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>188</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>170</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>373</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -17333,15 +17560,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>4386</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>253911</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -17449,7 +17676,9 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="110"/>
+      <c r="C47" s="110">
+        <v>4</v>
+      </c>
       <c r="D47" s="111"/>
       <c r="E47" s="112"/>
       <c r="F47" s="112"/>
@@ -17457,7 +17686,7 @@
       <c r="H47" s="73"/>
       <c r="I47" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="77">
         <f t="shared" si="7"/>
@@ -17489,7 +17718,7 @@
       </c>
       <c r="W47" s="129">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X47" s="27"/>
     </row>
@@ -17501,47 +17730,59 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2761</v>
+      </c>
+      <c r="D48" s="142">
+        <v>5</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
-      <c r="H48" s="139"/>
+      <c r="G48" s="143">
+        <v>3</v>
+      </c>
+      <c r="H48" s="139">
+        <v>2</v>
+      </c>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2758</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
       <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
+      <c r="N48" s="121">
+        <v>3</v>
+      </c>
+      <c r="O48" s="121">
+        <v>2</v>
+      </c>
       <c r="P48" s="121"/>
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16551</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -17553,7 +17794,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -17561,7 +17804,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -17593,7 +17836,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -17709,7 +17952,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -17717,7 +17962,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -17749,7 +17994,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -17813,7 +18058,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -17821,7 +18068,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -17853,7 +18100,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -18068,11 +18315,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>53740</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -18081,40 +18328,40 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>52803</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
@@ -18122,24 +18369,24 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>7260</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="W60" s="183">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>399073</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -18147,7 +18394,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -18165,7 +18412,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -18181,7 +18428,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -18197,7 +18444,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -18215,7 +18462,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -18231,7 +18478,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18626,17 +18873,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46218</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18661,62 +18908,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22052,7 +22299,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -22070,7 +22317,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -22086,7 +22333,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22102,7 +22349,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22120,7 +22367,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22136,7 +22383,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22160,6 +22407,3911 @@
         <v>3</v>
       </c>
       <c r="D69" s="205"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010E0CA0-54F0-45BB-BEF7-9C62312976A0}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="215">
+        <v>46219</v>
+      </c>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="218" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="219" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="220" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="221" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="225" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="227" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="225" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="229" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="209" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8+E8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80">
+        <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" ref="J14:J59" si="7">D14-H14</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="8">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146"/>
+      <c r="D41" s="147"/>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="187">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="79"/>
+      <c r="I44" s="188">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121"/>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>0</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>0</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="13">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>0</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="15">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="16">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
+        <v>0</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141"/>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="18">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="19">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="20">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>9</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="20"/>
+        <v>216</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>9</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>9</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="183">
+        <f>SUM(W8:W59)</f>
+        <v>216</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="210" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="211"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="212"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="213" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="213"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="214"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="207" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="208"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -22531,17 +26683,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46204</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22566,62 +26718,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="182" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26079,7 +30231,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26097,7 +30249,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26113,7 +30265,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26129,7 +30281,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26147,7 +30299,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26163,7 +30315,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26558,17 +30710,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46205</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26593,62 +30745,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30118,7 +34270,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30136,7 +34288,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30152,7 +34304,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30168,7 +34320,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30186,7 +34338,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30202,7 +34354,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30597,17 +34749,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46206</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30632,62 +34784,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34179,7 +38331,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34197,7 +38349,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34213,7 +38365,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34229,7 +38381,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34247,7 +38399,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34263,7 +38415,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34658,17 +38810,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46209</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -34693,62 +38845,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38214,7 +42366,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38232,7 +42384,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38248,7 +42400,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38264,7 +42416,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -38282,7 +42434,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -38298,7 +42450,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -38693,17 +42845,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46210</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -38728,62 +42880,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -42237,7 +46389,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -42255,7 +46407,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -42271,7 +46423,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -42287,7 +46439,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -42305,7 +46457,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -42321,7 +46473,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -42716,17 +46868,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46211</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -42751,62 +46903,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="197" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -46276,7 +50428,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -46294,7 +50446,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -46310,7 +50462,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -46326,7 +50478,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -46344,7 +50496,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -46360,7 +50512,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -46755,17 +50907,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46211</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -46790,62 +50942,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="200" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -50323,7 +54475,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -50341,7 +54493,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -50357,7 +54509,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -50373,7 +54525,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -50391,7 +54543,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -50407,7 +54559,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -50802,17 +54954,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="212">
+      <c r="P1" s="215">
         <v>46213</v>
       </c>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="213"/>
-      <c r="S1" s="213"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="213"/>
-      <c r="V1" s="213"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="214"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="217"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -50837,62 +54989,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="215" t="s">
+      <c r="B4" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="217" t="s">
+      <c r="D4" s="220" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="E4" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="220" t="s">
+      <c r="F4" s="222"/>
+      <c r="G4" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="224" t="s">
+      <c r="I4" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="226" t="s">
+      <c r="L4" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="227"/>
-      <c r="N4" s="227"/>
-      <c r="O4" s="227"/>
-      <c r="P4" s="227"/>
-      <c r="Q4" s="227"/>
-      <c r="R4" s="227"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
-      <c r="V4" s="228"/>
-      <c r="W4" s="227"/>
-      <c r="X4" s="229"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="231"/>
+      <c r="W4" s="230"/>
+      <c r="X4" s="232"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="203" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="221"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="223"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="226"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -54340,7 +58492,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="207" t="s">
+      <c r="G62" s="210" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -54358,7 +58510,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="208"/>
+      <c r="G63" s="211"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -54374,7 +58526,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="209"/>
+      <c r="G64" s="212"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -54390,7 +58542,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="210" t="s">
+      <c r="G65" s="213" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -54408,7 +58560,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="210"/>
+      <c r="G66" s="213"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -54424,7 +58576,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="211"/>
+      <c r="G67" s="214"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">

--- a/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/DSSR GBDS MONTH OF JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1143A541-84E9-4D88-B76D-2D2DAE1FD693}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3646CA7E-D077-4380-A6D7-49DA135DC6D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -27,9 +27,9 @@
     <sheet name="05,14" sheetId="127" r:id="rId12"/>
     <sheet name="05,15" sheetId="128" r:id="rId13"/>
     <sheet name="05,16" sheetId="129" r:id="rId14"/>
-    <sheet name="05,17" sheetId="130" r:id="rId15"/>
-    <sheet name="05,18" sheetId="131" r:id="rId16"/>
-    <sheet name="05,19" sheetId="132" r:id="rId17"/>
+    <sheet name="05,20" sheetId="130" r:id="rId15"/>
+    <sheet name="05,21" sheetId="131" r:id="rId16"/>
+    <sheet name="05,22" sheetId="132" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05,01'!$A$1:$Y$61</definedName>
@@ -45,9 +45,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="11">'05,14'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'05,15'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'05,16'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'05,17'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'05,18'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'05,19'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'05,20'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'05,21'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'05,22'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -27121,7 +27121,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="218">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="Q1" s="219"/>
       <c r="R1" s="219"/>
@@ -27375,19 +27375,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>40</v>
+      </c>
+      <c r="D8" s="111">
+        <v>9</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8+E8-G8</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -27415,7 +27419,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -27450,7 +27454,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>102</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -27458,7 +27464,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="80">
         <f t="shared" ref="I9:I59" si="4">C9+E9-G9</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -27490,7 +27496,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -27525,22 +27531,28 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>113</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>10</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
+      <c r="L10" s="112">
+        <v>10</v>
+      </c>
       <c r="M10" s="112"/>
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
@@ -27548,7 +27560,7 @@
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -27557,15 +27569,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -27600,30 +27612,38 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>86</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
-      <c r="G11" s="76"/>
+      <c r="G11" s="76">
+        <v>20</v>
+      </c>
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="41"/>
-      <c r="L11" s="112"/>
+      <c r="L11" s="112">
+        <v>10</v>
+      </c>
       <c r="M11" s="112"/>
       <c r="N11" s="112"/>
       <c r="O11" s="112"/>
-      <c r="P11" s="112"/>
+      <c r="P11" s="112">
+        <v>10</v>
+      </c>
       <c r="Q11" s="120"/>
       <c r="R11" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S11" s="124">
         <f t="shared" si="1"/>
@@ -27632,15 +27652,15 @@
       <c r="T11" s="41"/>
       <c r="U11" s="107">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="V11" s="130">
         <f>U11/24</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -27675,22 +27695,30 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
+      <c r="C12" s="110">
+        <v>10</v>
+      </c>
+      <c r="D12" s="111">
+        <v>2</v>
+      </c>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
-      <c r="G12" s="76"/>
+      <c r="G12" s="76">
+        <v>1</v>
+      </c>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="41"/>
-      <c r="L12" s="112"/>
+      <c r="L12" s="112">
+        <v>1</v>
+      </c>
       <c r="M12" s="112"/>
       <c r="N12" s="112"/>
       <c r="O12" s="112"/>
@@ -27698,7 +27726,7 @@
       <c r="Q12" s="120"/>
       <c r="R12" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="124">
         <f t="shared" si="1"/>
@@ -27707,15 +27735,15 @@
       <c r="T12" s="41"/>
       <c r="U12" s="107">
         <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V12" s="130">
         <f t="shared" ref="V12:V41" si="6">U12/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -27750,30 +27778,40 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="113">
+        <v>3688</v>
+      </c>
       <c r="D13" s="114"/>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
+      <c r="G13" s="78">
+        <v>32</v>
+      </c>
       <c r="H13" s="79"/>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3656</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
         <v>0</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
+      <c r="L13" s="121">
+        <v>10</v>
+      </c>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="N13" s="121">
+        <v>5</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
+      <c r="P13" s="121">
+        <v>17</v>
+      </c>
       <c r="Q13" s="122"/>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
@@ -27782,15 +27820,15 @@
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>87744</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -27832,19 +27870,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>2</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" ref="J14:J59" si="7">D14-H14</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -27872,7 +27914,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="9">I14*24+J14</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -27907,15 +27949,19 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>4</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
-      <c r="G15" s="76"/>
+      <c r="G15" s="76">
+        <v>2</v>
+      </c>
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="7"/>
@@ -27926,11 +27972,13 @@
       <c r="M15" s="112"/>
       <c r="N15" s="112"/>
       <c r="O15" s="112"/>
-      <c r="P15" s="112"/>
+      <c r="P15" s="112">
+        <v>2</v>
+      </c>
       <c r="Q15" s="120"/>
       <c r="R15" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S15" s="124">
         <f t="shared" si="8"/>
@@ -27939,15 +27987,15 @@
       <c r="T15" s="41"/>
       <c r="U15" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V15" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -28132,7 +28180,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -28140,7 +28190,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="7"/>
@@ -28172,7 +28222,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -28282,19 +28332,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -28322,7 +28376,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -28357,7 +28411,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
@@ -28365,7 +28421,7 @@
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="7"/>
@@ -28397,7 +28453,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -28432,7 +28488,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>2</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -28440,7 +28498,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="7"/>
@@ -28472,7 +28530,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -28508,7 +28566,9 @@
         <v>68</v>
       </c>
       <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
@@ -28519,7 +28579,7 @@
       </c>
       <c r="J23" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -28547,7 +28607,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -28589,19 +28649,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -28629,7 +28693,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -28671,22 +28735,28 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>8</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
-      <c r="G25" s="76"/>
+      <c r="G25" s="76">
+        <v>1</v>
+      </c>
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K25" s="41"/>
-      <c r="L25" s="112"/>
+      <c r="L25" s="112">
+        <v>1</v>
+      </c>
       <c r="M25" s="112"/>
       <c r="N25" s="112"/>
       <c r="O25" s="112"/>
@@ -28694,7 +28764,7 @@
       <c r="Q25" s="120"/>
       <c r="R25" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="124">
         <f t="shared" si="8"/>
@@ -28703,15 +28773,15 @@
       <c r="T25" s="41"/>
       <c r="U25" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V25" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -28746,19 +28816,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>93</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -28786,7 +28860,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2233</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -28802,11 +28876,15 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>3</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="76"/>
+      <c r="G27" s="76">
+        <v>3</v>
+      </c>
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
@@ -28817,7 +28895,9 @@
         <v>0</v>
       </c>
       <c r="K27" s="42"/>
-      <c r="L27" s="112"/>
+      <c r="L27" s="112">
+        <v>3</v>
+      </c>
       <c r="M27" s="112"/>
       <c r="N27" s="112"/>
       <c r="O27" s="112"/>
@@ -28825,7 +28905,7 @@
       <c r="Q27" s="120"/>
       <c r="R27" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" s="124">
         <f t="shared" si="8"/>
@@ -28834,11 +28914,11 @@
       <c r="T27" s="42"/>
       <c r="U27" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V27" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" s="129">
         <f t="shared" si="9"/>
@@ -28861,11 +28941,15 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>2</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
-      <c r="G28" s="76"/>
+      <c r="G28" s="76">
+        <v>2</v>
+      </c>
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
@@ -28880,11 +28964,13 @@
       <c r="M28" s="112"/>
       <c r="N28" s="112"/>
       <c r="O28" s="112"/>
-      <c r="P28" s="112"/>
+      <c r="P28" s="112">
+        <v>2</v>
+      </c>
       <c r="Q28" s="120"/>
       <c r="R28" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28" s="124">
         <f t="shared" si="8"/>
@@ -28893,11 +28979,11 @@
       <c r="T28" s="42"/>
       <c r="U28" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V28" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" s="129">
         <f t="shared" si="9"/>
@@ -28920,30 +29006,38 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>98</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>31</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
+      <c r="L29" s="112">
+        <v>30</v>
+      </c>
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>1</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="8"/>
@@ -28952,15 +29046,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1608</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -28979,30 +29073,40 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="111"/>
+      <c r="C30" s="110">
+        <v>14</v>
+      </c>
+      <c r="D30" s="111">
+        <v>5</v>
+      </c>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>11</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="41"/>
-      <c r="L30" s="112"/>
+      <c r="L30" s="112">
+        <v>10</v>
+      </c>
       <c r="M30" s="112"/>
       <c r="N30" s="112"/>
       <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
+      <c r="P30" s="112">
+        <v>1</v>
+      </c>
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="8"/>
@@ -29011,15 +29115,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -29031,7 +29135,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>1</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -29039,7 +29145,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="7"/>
@@ -29071,7 +29177,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -29135,22 +29241,28 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>5</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
-      <c r="G33" s="76"/>
+      <c r="G33" s="76">
+        <v>1</v>
+      </c>
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K33" s="41"/>
-      <c r="L33" s="112"/>
+      <c r="L33" s="112">
+        <v>1</v>
+      </c>
       <c r="M33" s="112"/>
       <c r="N33" s="112"/>
       <c r="O33" s="112"/>
@@ -29158,7 +29270,7 @@
       <c r="Q33" s="120"/>
       <c r="R33" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="124">
         <f t="shared" si="8"/>
@@ -29167,15 +29279,15 @@
       <c r="T33" s="41"/>
       <c r="U33" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V33" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -29187,22 +29299,28 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>5</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
-      <c r="G34" s="76"/>
+      <c r="G34" s="76">
+        <v>1</v>
+      </c>
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K34" s="41"/>
-      <c r="L34" s="112"/>
+      <c r="L34" s="112">
+        <v>1</v>
+      </c>
       <c r="M34" s="112"/>
       <c r="N34" s="112"/>
       <c r="O34" s="112"/>
@@ -29210,7 +29328,7 @@
       <c r="Q34" s="120"/>
       <c r="R34" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="124">
         <f t="shared" si="8"/>
@@ -29219,15 +29337,15 @@
       <c r="T34" s="41"/>
       <c r="U34" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V34" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -29239,30 +29357,40 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>282</v>
+      </c>
+      <c r="D35" s="111">
+        <v>14</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>12</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>10</v>
+      </c>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>2</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="8"/>
@@ -29271,15 +29399,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6494</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -29395,30 +29523,44 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
-      <c r="E38" s="115"/>
+      <c r="C38" s="113">
+        <v>2981</v>
+      </c>
+      <c r="D38" s="114">
+        <v>1</v>
+      </c>
+      <c r="E38" s="115">
+        <v>648</v>
+      </c>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>205</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3424</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>70</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>27</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>108</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="8"/>
@@ -29427,15 +29569,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>20545</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -29447,22 +29589,28 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>3</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
-      <c r="G39" s="76"/>
+      <c r="G39" s="76">
+        <v>1</v>
+      </c>
       <c r="H39" s="73"/>
       <c r="I39" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K39" s="41"/>
-      <c r="L39" s="112"/>
+      <c r="L39" s="112">
+        <v>1</v>
+      </c>
       <c r="M39" s="112"/>
       <c r="N39" s="112"/>
       <c r="O39" s="112"/>
@@ -29470,7 +29618,7 @@
       <c r="Q39" s="120"/>
       <c r="R39" s="96">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="126">
         <f t="shared" si="8"/>
@@ -29479,15 +29627,15 @@
       <c r="T39" s="41"/>
       <c r="U39" s="107">
         <f t="shared" ref="U39:U41" si="10">L39*24+N39*24+P39*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V39" s="109">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="11">I39*24+J39</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -29551,19 +29699,23 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>199</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
       <c r="G41" s="149"/>
       <c r="H41" s="150"/>
       <c r="I41" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
@@ -29591,7 +29743,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4796</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -29603,30 +29755,42 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>364</v>
+      </c>
       <c r="D42" s="164"/>
-      <c r="E42" s="165"/>
+      <c r="E42" s="165">
+        <v>288</v>
+      </c>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>114</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="187">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>60</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>14</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>40</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="8"/>
@@ -29635,15 +29799,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>6456</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -29698,30 +29862,44 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
-      <c r="E44" s="115"/>
+      <c r="C44" s="113">
+        <v>42757</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115">
+        <v>864</v>
+      </c>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1171</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="188">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42450</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>347</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>330</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>494</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="8"/>
@@ -29730,15 +29908,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>7026</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>254703</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -29794,11 +29972,15 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>2</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
-      <c r="G46" s="76"/>
+      <c r="G46" s="76">
+        <v>2</v>
+      </c>
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
@@ -29809,7 +29991,9 @@
         <v>0</v>
       </c>
       <c r="K46" s="41"/>
-      <c r="L46" s="112"/>
+      <c r="L46" s="112">
+        <v>2</v>
+      </c>
       <c r="M46" s="112"/>
       <c r="N46" s="112"/>
       <c r="O46" s="112"/>
@@ -29817,7 +30001,7 @@
       <c r="Q46" s="120"/>
       <c r="R46" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S46" s="128">
         <f t="shared" si="8"/>
@@ -29826,11 +30010,11 @@
       <c r="T46" s="41"/>
       <c r="U46" s="107">
         <f t="shared" ref="U46:U47" si="12">L46*24+N46*24+P46*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V46" s="134">
         <f t="shared" ref="V46:V47" si="13">U46/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="14">I46*24+J46</f>
@@ -29846,11 +30030,15 @@
       <c r="B47" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="110"/>
+      <c r="C47" s="110">
+        <v>3</v>
+      </c>
       <c r="D47" s="111"/>
       <c r="E47" s="112"/>
       <c r="F47" s="112"/>
-      <c r="G47" s="76"/>
+      <c r="G47" s="76">
+        <v>3</v>
+      </c>
       <c r="H47" s="73"/>
       <c r="I47" s="73">
         <f t="shared" si="4"/>
@@ -29861,15 +30049,19 @@
         <v>0</v>
       </c>
       <c r="K47" s="41"/>
-      <c r="L47" s="112"/>
+      <c r="L47" s="112">
+        <v>2</v>
+      </c>
       <c r="M47" s="112"/>
       <c r="N47" s="112"/>
       <c r="O47" s="112"/>
-      <c r="P47" s="112"/>
+      <c r="P47" s="112">
+        <v>1</v>
+      </c>
       <c r="Q47" s="120"/>
       <c r="R47" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S47" s="124">
         <f t="shared" si="8"/>
@@ -29878,11 +30070,11 @@
       <c r="T47" s="41"/>
       <c r="U47" s="107">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V47" s="130">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W47" s="129">
         <f t="shared" si="14"/>
@@ -29898,22 +30090,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2728</v>
+      </c>
+      <c r="D48" s="142">
+        <v>3</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>5</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2723</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
+      <c r="L48" s="121">
+        <v>5</v>
+      </c>
       <c r="M48" s="121"/>
       <c r="N48" s="121"/>
       <c r="O48" s="121"/>
@@ -29921,7 +30121,7 @@
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="8"/>
@@ -29930,15 +30130,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16341</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -29950,7 +30150,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -29958,7 +30160,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="7"/>
@@ -29990,7 +30192,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="17">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -30106,7 +30308,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -30114,7 +30318,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="78">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="7"/>
@@ -30146,7 +30350,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -30211,7 +30415,7 @@
         <v>78</v>
       </c>
       <c r="C54" s="110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
@@ -30220,7 +30424,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="7"/>
@@ -30252,7 +30456,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -30467,20 +30671,20 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>9</v>
+        <v>53686</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1628</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
@@ -30488,16 +30692,16 @@
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>9</v>
+        <v>53858</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="21">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="21"/>
@@ -30505,7 +30709,7 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="21"/>
@@ -30513,7 +30717,7 @@
       </c>
       <c r="P60" s="74">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="21"/>
@@ -30521,7 +30725,7 @@
       </c>
       <c r="R60" s="85">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1628</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="21"/>
@@ -30530,15 +30734,15 @@
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>12846</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1628</v>
       </c>
       <c r="W60" s="183">
         <f>SUM(W8:W59)</f>
-        <v>216</v>
+        <v>410911</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -31026,7 +31230,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="218">
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="Q1" s="219"/>
       <c r="R1" s="219"/>
@@ -34931,7 +35135,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="218">
-        <v>46222</v>
+        <v>46225</v>
       </c>
       <c r="Q1" s="219"/>
       <c r="R1" s="219"/>
